--- a/out/MLP-S4_repeat_5_000001.xlsx
+++ b/out/MLP-S4_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.7133722983876</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.7133722983876</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004032911647059955</v>
+        <v>-0.0002535016661258414</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1736453593267007</v>
+        <v>0.109150457288626</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3477543471779763</v>
+        <v>0.218592208289315</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6708838559935975</v>
+        <v>0.4217059410812483</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.7133722983876</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.516322198248013</v>
+        <v>0.9531327588277774</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2063676348851421</v>
+        <v>0.129718602426742</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.7133722983876</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.257323691988448</v>
+        <v>0.7903311976263911</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04187352821453396</v>
+        <v>0.02632086936349905</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.7133722983876</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.134379665258729</v>
+        <v>0.7130507957494254</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0362646942024548</v>
+        <v>0.02279540043239606</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.164988820114564</v>
+        <v>0.7322912155897435</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01772863612664385</v>
+        <v>0.01114415392182735</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.164135320544757</v>
+        <v>0.7317547189947436</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008460734312728226</v>
+        <v>0.005316318710857742</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.163304628310009</v>
+        <v>0.7312307124471878</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003521759136262648</v>
+        <v>0.00221182002850795</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.161877692872072</v>
+        <v>0.7303319244576276</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002438883608912729</v>
+        <v>0.001531397936642009</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.163231280085747</v>
+        <v>0.7311808930841831</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001015550645484366</v>
+        <v>0.0006360655885460508</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.162820068591475</v>
+        <v>0.7309206011294995</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005241919159969026</v>
+        <v>0.0003277494623313857</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.162851838176052</v>
+        <v>0.7309387213985892</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002028461782342921</v>
+        <v>0.0001256911575261079</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.162732715906819</v>
+        <v>0.7308619626989958</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000108381385744506</v>
+        <v>6.600652440565022e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.162746400690367</v>
+        <v>0.7308687121071785</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.090250148663969e-05</v>
+        <v>3.000964739567334e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.162739696092184</v>
+        <v>0.7308626366099494</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.110845516429424e-05</v>
+        <v>1.151759408353309e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.162731478890827</v>
+        <v>0.7308555895250333</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.529296331733944e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.162722863107682</v>
+        <v>0.730848275423821</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.16271665431271</v>
+        <v>0.7308425014448842</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.162710404945275</v>
+        <v>0.7308367323020166</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.162704453934516</v>
+        <v>0.7308311886339141</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.162699611627073</v>
+        <v>0.7308262674801927</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.162694690425525</v>
+        <v>0.730826307335665</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.16269468245443</v>
+        <v>0.7308262993645706</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.16269484187632</v>
+        <v>0.7308264587864597</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.162695096951343</v>
+        <v>0.7308267138614825</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.162694849847414</v>
+        <v>0.7308264667575541</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.162694809991942</v>
+        <v>0.7308264269020818</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.162694817963036</v>
+        <v>0.7308264348731762</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.7133722983876</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.162694849847414</v>
+        <v>0.7308264667575541</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.7133722983876</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.162694945500548</v>
+        <v>0.7308265624106878</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.162694881731792</v>
+        <v>0.7308264986419319</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.16269484187632</v>
+        <v>0.7308264587864597</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.162694817963036</v>
+        <v>0.7308264348731762</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.162694570859108</v>
+        <v>0.7308261877692481</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.162694491148164</v>
+        <v>0.7308261080583034</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.16269453897473</v>
+        <v>0.7308261558848701</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.162694658541147</v>
+        <v>0.7308262754512872</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.162694642598958</v>
+        <v>0.7308262595090983</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.162694658541147</v>
+        <v>0.7308262754512872</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.162694642598958</v>
+        <v>0.7308262595090983</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.162694698396619</v>
+        <v>0.7308263153067595</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.162694698396619</v>
+        <v>0.7308263153067595</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.162694698396619</v>
+        <v>0.7308263153067595</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.162694849847414</v>
+        <v>0.7308264667575541</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.162695065066964</v>
+        <v>0.7308266819771047</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.162694977384925</v>
+        <v>0.7308265942950656</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.162694929558359</v>
+        <v>0.7308265464684989</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.162694977384925</v>
+        <v>0.7308265942950656</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.162694794049753</v>
+        <v>0.7308264109598929</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.162694802020847</v>
+        <v>0.7308264189309873</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.162694809991942</v>
+        <v>0.7308264269020818</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.162694817963036</v>
+        <v>0.7308264348731762</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.162694817963036</v>
+        <v>0.7308264348731762</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.7133722983876</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.162694857818509</v>
+        <v>0.7308264747286486</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.162694921587264</v>
+        <v>0.7308265384974044</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.162695033182586</v>
+        <v>0.7308266500927268</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.162695081009153</v>
+        <v>0.7308266979192936</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.162695041153681</v>
+        <v>0.7308266580638213</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.162694969413831</v>
+        <v>0.7308265863239711</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.162695088980248</v>
+        <v>0.730826705890388</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.162694929558359</v>
+        <v>0.7308265464684989</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.162694698396619</v>
+        <v>0.7308263153067595</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.162694650570053</v>
+        <v>0.7308262674801927</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.16269468245443</v>
+        <v>0.7308262993645706</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.162694666512242</v>
+        <v>0.7308262834223817</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.162694546945825</v>
+        <v>0.7308261638559646</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.162694507090352</v>
+        <v>0.7308261240004923</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.162694650570053</v>
+        <v>0.7308262674801927</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.162694786078659</v>
+        <v>0.7308264029887984</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.16269477013647</v>
+        <v>0.7308263870466095</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.162694706367714</v>
+        <v>0.7308263232778539</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.162694602743486</v>
+        <v>0.7308262196536259</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.162694483177069</v>
+        <v>0.7308261000872089</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.162694602743486</v>
+        <v>0.7308262196536259</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.162694650570053</v>
+        <v>0.7308262674801927</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.162694746223186</v>
+        <v>0.7308263631333262</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.162694626656769</v>
+        <v>0.7308262435669093</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8742121623455774</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.162694634627864</v>
+        <v>0.7308262515380038</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000001.xlsx
+++ b/out/MLP-S4_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.7133722983876</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.7133722983876</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004032911647059955</v>
+        <v>-0.0003042373122241115</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1736453593267007</v>
+        <v>0.1309957534442411</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3477543471779763</v>
+        <v>0.2623410999202765</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6708838559935975</v>
+        <v>0.5061050457091908</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.516322198248013</v>
+        <v>1.143892083945366</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2063676348851421</v>
+        <v>0.1556812581509435</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.7133722983876</v>
+        <v>2.500598147465783</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.257323691988448</v>
+        <v>0.9485072114088153</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04187352821453396</v>
+        <v>0.03158867877245474</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.134379665258729</v>
+        <v>0.8557601761445718</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0362646942024548</v>
+        <v>0.02735719970903234</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.164988820114564</v>
+        <v>0.8788512779824748</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01772863612664385</v>
+        <v>0.01337466388558837</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.164135320544757</v>
+        <v>0.8782074012302132</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008460734312728226</v>
+        <v>0.006381384258962619</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.163304628310009</v>
+        <v>0.877579515170251</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003521759136262648</v>
+        <v>0.002655518060331365</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.161877692872072</v>
+        <v>0.8765018349085462</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002438883608912729</v>
+        <v>0.001838523189672405</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.163231280085747</v>
+        <v>0.8775217266970777</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001015550645484366</v>
+        <v>0.0007649229932789252</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.162820068591475</v>
+        <v>0.8772102729498206</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005241919159969026</v>
+        <v>0.0003938984518309985</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.162851838176052</v>
+        <v>0.8772330133302656</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002028461782342921</v>
+        <v>0.0001519343618486195</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.162732715906819</v>
+        <v>0.877141845253244</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000108381385744506</v>
+        <v>8.032235593904744e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.162746400690367</v>
+        <v>0.8771509538512688</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.090250148663969e-05</v>
+        <v>3.735037991412098e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.162739696092184</v>
+        <v>0.8771446624890094</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.110845516429424e-05</v>
+        <v>1.471454777712014e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.162731478890827</v>
+        <v>0.8771372253652793</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.529296331733944e-06</v>
+        <v>3.762265212117796e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.162722863107682</v>
+        <v>0.8771294773700898</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.16271665431271</v>
+        <v>0.877123558817219</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.410678356938051e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.162710404945275</v>
+        <v>0.8771175973886345</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.162704453934516</v>
+        <v>0.8771119182119262</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.162699611627073</v>
+        <v>0.8771070369136769</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.162694690425525</v>
+        <v>0.877102115712129</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.16269468245443</v>
+        <v>0.8771021077410346</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.16269484187632</v>
+        <v>0.8771022671629237</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.162695096951343</v>
+        <v>0.8771025222379465</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.162694849847414</v>
+        <v>0.8771022751340182</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.162694809991942</v>
+        <v>0.8771022352785459</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.162694817963036</v>
+        <v>0.8771022432496404</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.162694849847414</v>
+        <v>0.8771022751340182</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.7133722983876</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.162694945500548</v>
+        <v>0.8771023707871518</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.162694881731792</v>
+        <v>0.877102307018396</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.16269484187632</v>
+        <v>0.8771022671629237</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.162694817963036</v>
+        <v>0.8771022432496404</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.162694570859108</v>
+        <v>0.8771019961457122</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.162694491148164</v>
+        <v>0.8771019164347674</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.16269453897473</v>
+        <v>0.8771019642613341</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.162694658541147</v>
+        <v>0.8771020838277512</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.162694642598958</v>
+        <v>0.8771020678855623</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.162694658541147</v>
+        <v>0.8771020838277512</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.162694642598958</v>
+        <v>0.8771020678855623</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.162694698396619</v>
+        <v>0.8771021236832235</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.162694698396619</v>
+        <v>0.8771021236832235</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.7133722983876</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.162694698396619</v>
+        <v>0.8771021236832235</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2742121623455775</v>
+        <v>1.589150270726771</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.162694849847414</v>
+        <v>0.8771022751340182</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.7133722983876</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.162695065066964</v>
+        <v>0.8771024903535687</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.162694977384925</v>
+        <v>0.8771024026715297</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.162694929558359</v>
+        <v>0.8771023548449629</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.162694977384925</v>
+        <v>0.8771024026715297</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.162694794049753</v>
+        <v>0.877102219336357</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.162694802020847</v>
+        <v>0.8771022273074515</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.162694809991942</v>
+        <v>0.8771022352785459</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.162694817963036</v>
+        <v>0.8771022432496404</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8742121623455774</v>
+        <v>0.4777023939877588</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.162694817963036</v>
+        <v>0.8771022432496404</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.7133722983876</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.162694857818509</v>
+        <v>0.8771022831051126</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2742121623455775</v>
+        <v>0.6777023939877589</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.162694921587264</v>
+        <v>0.8771023468738685</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2742121623455775</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.162695033182586</v>
+        <v>0.8771024584691909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.2337454827512531</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.162695081009153</v>
+        <v>0.8771025062957576</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.162695041153681</v>
+        <v>0.8771024664402853</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.162694969413831</v>
+        <v>0.8771023947004353</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.162695088980248</v>
+        <v>0.877102514266852</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.162694929558359</v>
+        <v>0.8771023548449629</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.162694698396619</v>
+        <v>0.8771021236832235</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.162694650570053</v>
+        <v>0.8771020758566568</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.16269468245443</v>
+        <v>0.8771021077410346</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.162694666512242</v>
+        <v>0.8771020917988457</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.162694546945825</v>
+        <v>0.8771019722324286</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.162694507090352</v>
+        <v>0.8771019323769563</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.162694650570053</v>
+        <v>0.8771020758566568</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.162694786078659</v>
+        <v>0.8771022113652626</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.16269477013647</v>
+        <v>0.8771021954230735</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.162694706367714</v>
+        <v>0.8771021316543179</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.162694602743486</v>
+        <v>0.8771020280300901</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.162694483177069</v>
+        <v>0.877101908463673</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.162694602743486</v>
+        <v>0.8771020280300901</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.162694650570053</v>
+        <v>0.8771020758566568</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.162694746223186</v>
+        <v>0.8771021715097902</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.162694626656769</v>
+        <v>0.8771020519433734</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8742121623455774</v>
+        <v>-0.4337454827512531</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.162694634627864</v>
+        <v>0.8771020599144679</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000001.xlsx
+++ b/out/MLP-S4_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3367774784564972</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4507996141910553</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3692500293254852</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3413003385066986</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3764244318008423</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4795893132686615</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3460385799407959</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3471310436725616</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4027744233608246</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3302890062332153</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3764105141162872</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3475886881351471</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4242879152297974</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.526385486125946</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.589150270726771</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5709776878356934</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.500598147465783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5752564668655396</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.589150270726771</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4635637998580933</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4871265888214111</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4771521687507629</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4070650637149811</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4017673432826996</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4378727376461029</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4832860231399536</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4777023939877588</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5224165916442871</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4777023939877588</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4511252045631409</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4340179562568665</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4253825545310974</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3803789615631104</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4292741715908051</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4777023939877588</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5563938617706299</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6777023939877589</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3993526995182037</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6777023939877589</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4487555921077728</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3755603134632111</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3655800223350525</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3489256799221039</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4012812972068787</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4255000352859497</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4527648389339447</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4777023939877588</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6067273616790771</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.589150270726771</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.651172935962677</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.500598147465783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7511987686157227</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.500598147465783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7905909419059753</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.500598147465783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003042373122241115</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1309957534442411</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8863723278045654</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.500598147465783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2623410999202765</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5061050457091908</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.886522114276886</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.500598147465783</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.143892083945366</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1556812581509435</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6664011478424072</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.500598147465783</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9485072114088153</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03158867877245474</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5823293924331665</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.589150270726771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8557601761445718</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02735719970903234</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3683373034000397</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4777023939877588</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8788512779824748</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01337466388558837</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.419709175825119</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8782074012302132</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006381384258962619</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3722653687000275</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.877579515170251</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002655518060331365</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3641751408576965</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8765018349085462</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001838523189672405</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.341687023639679</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8775217266970777</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007649229932789252</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.48016756772995</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8772102729498206</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003938984518309985</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4981249868869781</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8772330133302656</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001519343618486195</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3727861344814301</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.877141845253244</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.032235593904744e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3889103531837463</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8771509538512688</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.735037991412098e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3033004403114319</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8771446624890094</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3195472359657288</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8771372253652793</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.762265212117796e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3036250174045563</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8771294773700898</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.2883728444576263</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.877123558817219</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2917087972164154</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8771175973886345</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.2894359827041626</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8771119182119262</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3257724642753601</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8771070369136769</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.2634066641330719</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.877102115712129</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3521949648857117</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8771021077410346</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3450000882148743</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8771022671629237</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4719657003879547</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.408012181520462</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8771025222379465</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3678191304206848</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8771022751340182</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.431303083896637</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8771022352785459</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.358858048915863</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.364747166633606</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8771022432496404</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3831615746021271</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7064084410667419</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.589150270726771</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8771022751340182</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5052979588508606</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.589150270726771</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8771023707871518</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3748640120029449</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.877102307018396</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3307580947875977</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8771022671629237</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4439615309238434</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8771022432496404</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3855793178081512</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8771019961457122</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3435811996459961</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8771019164347674</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3490082919597626</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8771019642613341</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3122057914733887</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8771020838277512</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.385677695274353</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8771020678855623</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3852057456970215</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8771020838277512</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4210644960403442</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8771020678855623</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.420974463224411</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8771021236832235</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3715861141681671</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8771021236832235</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5338217616081238</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8771021236832235</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3709103465080261</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.589150270726771</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8771022751340182</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5298619866371155</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8771024903535687</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.349187970161438</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6777023939877589</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8771024026715297</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3571666777133942</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2337454827512531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8771023548449629</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3999706208705902</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8771024026715297</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3303492069244385</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.877102219336357</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3293539881706238</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8771022273074515</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4089327752590179</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8771022352785459</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3358795642852783</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8771022432496404</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3470903038978577</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4777023939877588</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8771022432496404</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5204355120658875</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8771022831051126</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4792979657649994</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6777023939877589</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8771023468738685</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4904115796089172</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8771024584691909</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4022966027259827</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2337454827512531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8771025062957576</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4412819743156433</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8771024664402853</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4502813220024109</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8771023947004353</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4386107921600342</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.877102514266852</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4661605656147003</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8771023548449629</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3669250309467316</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8771021236832235</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3485225737094879</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8771020758566568</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3112106919288635</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8771021077410346</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3653377592563629</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3072781562805176</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3232541680335999</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8771020917988457</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3510598540306091</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8771019722324286</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3565421402454376</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8771019323769563</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4132573306560516</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8771020758566568</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3931695222854614</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8771022113652626</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3375536501407623</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8771021954230735</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3465370237827301</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3347266316413879</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8771021316543179</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3749574422836304</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8771020280300901</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4103234708309174</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.877101908463673</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3193889260292053</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8771020280300901</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3575454950332642</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8771020758566568</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3062916398048401</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4337454827512531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8771021715097902</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3426262438297272</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.1600000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8771020519433734</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4296448528766632</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4337454827512531</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8771020599144679</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000001.xlsx
+++ b/out/MLP-S4_repeat_5_000001.xlsx
@@ -42284,7 +42284,7 @@
         <v>0.341687023639679</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0.5240054028804111</v>
@@ -43079,7 +43079,7 @@
         <v>0.48016756772995</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0.5238174288811471</v>
@@ -43874,7 +43874,7 @@
         <v>0.4981249868869781</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0.5238290030499527</v>
@@ -44669,7 +44669,7 @@
         <v>0.3727861344814301</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0.5237725621866074</v>
@@ -45464,7 +45464,7 @@
         <v>0.3889103531837463</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0.5237760087290115</v>
